--- a/results/comparison_SimpleRAG/SimpleRAG_costs.xlsx
+++ b/results/comparison_SimpleRAG/SimpleRAG_costs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,13 +472,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>45.85231900215149</v>
+        <v>13.52766251564026</v>
       </c>
       <c r="B2" t="n">
-        <v>41.640625</v>
+        <v>1979.00390625</v>
       </c>
       <c r="C2" t="n">
-        <v>24.4</v>
+        <v>8.1</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -487,12 +487,1728 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.912904024124146</v>
+        <v>1.287301540374756</v>
       </c>
       <c r="G2" t="n">
-        <v>43.93941211700439</v>
+        <v>12.24035620689392</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6.048534393310547</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1979.19921875</v>
+      </c>
+      <c r="C3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2426419258117676</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.805888175964355</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8.950906753540039</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1979.22265625</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2817859649658203</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8.669118165969849</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>14.49628663063049</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1979.34375</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2692399024963379</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14.22704386711121</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9.378642320632935</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1979.43359375</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2917795181274414</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9.086860418319702</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>23.02340173721313</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1979.625</v>
+      </c>
+      <c r="C7" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2402205467224121</v>
+      </c>
+      <c r="G7" t="n">
+        <v>22.78317904472351</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>12.83068776130676</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1979.77734375</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2401654720306396</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12.59052014350891</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>23.54131126403809</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1979.890625</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2397725582122803</v>
+      </c>
+      <c r="G9" t="n">
+        <v>23.30153656005859</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>20.72910737991333</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1979.9453125</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2396740913391113</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20.48943209648132</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6.231470108032227</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1980.0546875</v>
+      </c>
+      <c r="C11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2392227649688721</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.992245197296143</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>17.93051409721375</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1980.15625</v>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2370893955230713</v>
+      </c>
+      <c r="G12" t="n">
+        <v>17.69342303276062</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6.730621337890625</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1980.21875</v>
+      </c>
+      <c r="C13" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2393231391906738</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6.491296291351318</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12.35335683822632</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1980.2265625</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.239429235458374</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12.113924741745</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3.868642330169678</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1980.2265625</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2472937107086182</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.621345996856689</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>10.57109951972961</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1980.2265625</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2388803958892822</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10.33221745491028</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>14.71281695365906</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1980.2265625</v>
+      </c>
+      <c r="C17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5229270458221436</v>
+      </c>
+      <c r="G17" t="n">
+        <v>14.1898877620697</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6.178676128387451</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1980.30078125</v>
+      </c>
+      <c r="C18" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2393403053283691</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.939333438873291</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>22.11004209518433</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1980.30078125</v>
+      </c>
+      <c r="C19" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2384488582611084</v>
+      </c>
+      <c r="G19" t="n">
+        <v>21.87159085273743</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6.994408369064331</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1980.375</v>
+      </c>
+      <c r="C20" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2374808788299561</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6.756925344467163</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>18.77078199386597</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1980.703125</v>
+      </c>
+      <c r="C21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2397530078887939</v>
+      </c>
+      <c r="G21" t="n">
+        <v>18.53102684020996</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8.732227325439453</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1980.76953125</v>
+      </c>
+      <c r="C22" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2387099266052246</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8.493514776229858</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>19.86621689796448</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1980.7890625</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.2376730442047119</v>
+      </c>
+      <c r="G23" t="n">
+        <v>19.62854194641113</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.616020441055298</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1980.79296875</v>
+      </c>
+      <c r="C24" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.2416989803314209</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4.374318838119507</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.538184404373169</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1980.79296875</v>
+      </c>
+      <c r="C25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.2385787963867188</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4.299603700637817</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9.611172676086426</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1980.79296875</v>
+      </c>
+      <c r="C26" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.2390704154968262</v>
+      </c>
+      <c r="G26" t="n">
+        <v>9.372099876403809</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.291810512542725</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1980.796875</v>
+      </c>
+      <c r="C27" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.2404916286468506</v>
+      </c>
+      <c r="G27" t="n">
+        <v>7.051316738128662</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6.826941967010498</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1980.796875</v>
+      </c>
+      <c r="C28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.2400681972503662</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6.586871385574341</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3.277172803878784</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1980.796875</v>
+      </c>
+      <c r="C29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.2410519123077393</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.036118507385254</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.63473606109619</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1980.80859375</v>
+      </c>
+      <c r="C30" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.240105152130127</v>
+      </c>
+      <c r="G30" t="n">
+        <v>11.39462876319885</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3.787538528442383</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1980.83203125</v>
+      </c>
+      <c r="C31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.2387039661407471</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.548832893371582</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>4.011513233184814</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1980.84375</v>
+      </c>
+      <c r="C32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.2378706932067871</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3.773640155792236</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>11.57422685623169</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1981.05078125</v>
+      </c>
+      <c r="C33" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.2392501831054688</v>
+      </c>
+      <c r="G33" t="n">
+        <v>11.33497381210327</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>10.83628010749817</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1981.08984375</v>
+      </c>
+      <c r="C34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.2381119728088379</v>
+      </c>
+      <c r="G34" t="n">
+        <v>10.59816598892212</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6.935172080993652</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1981.08984375</v>
+      </c>
+      <c r="C35" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.2380862236022949</v>
+      </c>
+      <c r="G35" t="n">
+        <v>6.697083473205566</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>6.440232276916504</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1981.1015625</v>
+      </c>
+      <c r="C36" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.2392868995666504</v>
+      </c>
+      <c r="G36" t="n">
+        <v>6.200943470001221</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6.906960248947144</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1981.1015625</v>
+      </c>
+      <c r="C37" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.2409083843231201</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6.666049480438232</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4.317200899124146</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1981.1015625</v>
+      </c>
+      <c r="C38" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.2396895885467529</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4.077508449554443</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>6.231205224990845</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1981.109375</v>
+      </c>
+      <c r="C39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.2374768257141113</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5.993726015090942</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>235.5037314891815</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1982.76953125</v>
+      </c>
+      <c r="C40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.241093635559082</v>
+      </c>
+      <c r="G40" t="n">
+        <v>235.2626357078552</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>7.313881635665894</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1982.76953125</v>
+      </c>
+      <c r="C41" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.184974670410156</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6.128904342651367</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>9.197699546813965</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1982.76953125</v>
+      </c>
+      <c r="C42" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.2414143085479736</v>
+      </c>
+      <c r="G42" t="n">
+        <v>8.9562828540802</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>3.929612874984741</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1982.76953125</v>
+      </c>
+      <c r="C43" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.2389669418334961</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3.690644264221191</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>8.929407596588135</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1982.76953125</v>
+      </c>
+      <c r="C44" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.2379782199859619</v>
+      </c>
+      <c r="G44" t="n">
+        <v>8.691426992416382</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>5.48317551612854</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1982.76953125</v>
+      </c>
+      <c r="C45" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.2370724678039551</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5.246101140975952</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.30503511428833</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1982.76953125</v>
+      </c>
+      <c r="C46" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.23885178565979</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4.066181182861328</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>6.624162673950195</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1982.76953125</v>
+      </c>
+      <c r="C47" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.2392404079437256</v>
+      </c>
+      <c r="G47" t="n">
+        <v>6.384920358657837</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>8.376982450485229</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1982.7734375</v>
+      </c>
+      <c r="C48" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.240056037902832</v>
+      </c>
+      <c r="G48" t="n">
+        <v>8.136924028396606</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4.600898027420044</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1982.7734375</v>
+      </c>
+      <c r="C49" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.2411856651306152</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.359710454940796</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>9.03327465057373</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1982.7734375</v>
+      </c>
+      <c r="C50" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.2377574443817139</v>
+      </c>
+      <c r="G50" t="n">
+        <v>8.795514822006226</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>10.68616223335266</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1982.7734375</v>
+      </c>
+      <c r="C51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.2373921871185303</v>
+      </c>
+      <c r="G51" t="n">
+        <v>10.4487681388855</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>7.171700477600098</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1982.7734375</v>
+      </c>
+      <c r="C52" t="n">
+        <v>11</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.2856950759887695</v>
+      </c>
+      <c r="G52" t="n">
+        <v>6.886003494262695</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>10.82754445075989</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1982.7734375</v>
+      </c>
+      <c r="C53" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.2369425296783447</v>
+      </c>
+      <c r="G53" t="n">
+        <v>10.59059977531433</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>9.729821920394897</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1982.7734375</v>
+      </c>
+      <c r="C54" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.2394542694091797</v>
+      </c>
+      <c r="G54" t="n">
+        <v>9.490365505218506</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>8.387143611907959</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1982.7734375</v>
+      </c>
+      <c r="C55" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.2404484748840332</v>
+      </c>
+      <c r="G55" t="n">
+        <v>8.146693468093872</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>5.270350217819214</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1982.7734375</v>
+      </c>
+      <c r="C56" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.2369580268859863</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5.033390283584595</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>6.532838344573975</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1982.7734375</v>
+      </c>
+      <c r="C57" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.2402403354644775</v>
+      </c>
+      <c r="G57" t="n">
+        <v>6.292595863342285</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4.140222072601318</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1982.7734375</v>
+      </c>
+      <c r="C58" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.2364885807037354</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3.903730630874634</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>232.1709263324738</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1983.98828125</v>
+      </c>
+      <c r="C59" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.2390356063842773</v>
+      </c>
+      <c r="G59" t="n">
+        <v>231.9318885803223</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>6.843535661697388</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1983.98828125</v>
+      </c>
+      <c r="C60" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.258098602294922</v>
+      </c>
+      <c r="G60" t="n">
+        <v>5.585434913635254</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>7.10402774810791</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1983.98828125</v>
+      </c>
+      <c r="C61" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.2431316375732422</v>
+      </c>
+      <c r="G61" t="n">
+        <v>6.860893487930298</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>8.694788455963135</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1983.98828125</v>
+      </c>
+      <c r="C62" t="n">
+        <v>9</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.242121696472168</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8.452664136886597</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>8.630897760391235</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1983.98828125</v>
+      </c>
+      <c r="C63" t="n">
+        <v>11</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.2406463623046875</v>
+      </c>
+      <c r="G63" t="n">
+        <v>8.390245914459229</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>5.876294612884521</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1983.98828125</v>
+      </c>
+      <c r="C64" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.2432882785797119</v>
+      </c>
+      <c r="G64" t="n">
+        <v>5.633004188537598</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>10.66517162322998</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1983.98828125</v>
+      </c>
+      <c r="C65" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.2433154582977295</v>
+      </c>
+      <c r="G65" t="n">
+        <v>10.4218533039093</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>3.810158252716064</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1983.98828125</v>
+      </c>
+      <c r="C66" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.2418458461761475</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3.568310260772705</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3.520079851150513</v>
+      </c>
+      <c r="B67" t="n">
+        <v>1983.98828125</v>
+      </c>
+      <c r="C67" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.3050332069396973</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3.215044736862183</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>5.97469162940979</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1983.98828125</v>
+      </c>
+      <c r="C68" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.2403542995452881</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5.734334945678711</v>
+      </c>
+      <c r="H68" t="n">
         <v>0</v>
       </c>
     </row>
